--- a/КПП/Том СПС КПП/Реестр документов о качестве СПС КПП.xlsx
+++ b/КПП/Том СПС КПП/Реестр документов о качестве СПС КПП.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="94">
   <si>
     <t xml:space="preserve">Объект капитального строительства: «Центр временного содержания иностранных граждан», Калужская область, м. р-н Боровский, д. Старомихайловское, ул. 1-я Индустриальная, вл. 2, земельный участок с кадастровым номером 40:03:068314:1874</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Лицо, выполнившее работы: ООО «АльтЭн», ОГРН 1024000944098, ИНН 4025062969</t>
   </si>
   <si>
-    <t xml:space="preserve">Здание: КПП. Том ИД: СПС — система пожарной сигнализации и система оповещения и управления эвакуацией (АПС, СОУЭ). Рабочая документация 16/1/26-АПС,СОУЭ-Р. Исполнительная документация 16/1/26-ИД-КПП, лист 2; кабельный журнал 16/1/26-ИД-КПП.КЖ (раздел СПС)</t>
+    <t xml:space="preserve">Здание: КПП. Том ИД: СПС — система пожарной сигнализации и система оповещения и управления эвакуацией (АПС, СОУЭ). Рабочая документация 16/1/26-АПС,СОУЭ-Р. Исполнительная документация 16/1/26-АПС,СОУЭ-ИД-КПП, лист 2; кабельный журнал 16/1/26-АПС,СОУЭ-ИД-КПП.КЖ; спецификация 16/1/26-АПС,СОУЭ-ИД-КПП.СО</t>
   </si>
   <si>
     <t xml:space="preserve">РЕЕСТР</t>
@@ -163,15 +163,42 @@
     <t xml:space="preserve">Кабель-канал магистральный 25×16 ЭЛЕКОР</t>
   </si>
   <si>
-    <t xml:space="preserve">IEK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Предоставить</t>
+    <t xml:space="preserve">АО «ИЭК ХОЛДИНГ» (IEK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СЕРТИФИКАТ СООТВЕТСТВИЯ (ТР ЕАЭС 043/2017) с приложениями № 1–2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЕАЭС RU C-RU.НВ88.В.00177/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.02.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">по 27.09.2028 включительно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОС ООО «Национальная Лаборатория» (RA.RU.11НВ88)</t>
   </si>
   <si>
     <t xml:space="preserve">2-СПС-КПП</t>
   </si>
   <si>
+    <t xml:space="preserve">РЕШЕНИЕ органа по сертификации об отказе (ТР ТС 004/2011, ТР ТС 020/2011, ТР ЕАЭС 037/2016 не распространяются)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">№ 3035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.11.2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОС ООО «НИЦ ТЕСТ» (RA.RU.11НВ63)</t>
+  </si>
+  <si>
     <t xml:space="preserve">АОСР № 3-СПС-КПП — прокладка кабельных линий</t>
   </si>
   <si>
@@ -205,9 +232,6 @@
     <t xml:space="preserve">«Промрукав» (ООО «НЕПТУН»)</t>
   </si>
   <si>
-    <t xml:space="preserve">СЕРТИФИКАТ СООТВЕТСТВИЯ (ТР ЕАЭС 043/2017) с приложениями № 1–2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ЕАЭС RU C-RU.ПБ74.В.00766/23</t>
   </si>
   <si>
@@ -220,6 +244,9 @@
     <t xml:space="preserve">ОС «СЗРЦ СЕРТ»</t>
   </si>
   <si>
+    <t xml:space="preserve">ПАСПОРТ изготовителя (труба гофрированная ПВХ серая)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Скоба металлическая однолапковая СМО 19-20, арт. PR08.2534</t>
   </si>
   <si>
@@ -232,13 +259,28 @@
     <t xml:space="preserve">ПАСПОРТ</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
     <t xml:space="preserve">Изготовитель «Промрукав»</t>
   </si>
   <si>
     <t xml:space="preserve">Коробка огнестойкая 40-0300-FR6.0-4, Е15–Е120, 100×100×50 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СЕРТИФИКАТ СООТВЕТСТВИЯ (ТР ТС 004/2011) с приложением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЕАЭС RU C-RU.0010.В.00450/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.12.2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">по 26.12.2029 включительно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОС ООО «Центр охраны труда и экологии «ЭКСПЕРТЭГИДА»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПАСПОРТ изготовителя (коробка огнестойкая 100×100×50)</t>
   </si>
   <si>
     <t xml:space="preserve">Представитель лица, осуществляющего строительство</t>
@@ -330,13 +372,6 @@
     </font>
     <font>
       <i val="true"/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="0"/>
@@ -349,19 +384,20 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -405,7 +441,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -442,23 +478,11 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -466,11 +490,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -483,66 +507,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -726,7 +690,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1076,7 +1040,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
         <v>4</v>
       </c>
@@ -1092,81 +1056,91 @@
       <c r="E17" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="11"/>
+      <c r="G17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="L17" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="B18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="F19" s="8" t="s">
+      <c r="E18" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>22</v>
@@ -1175,205 +1149,329 @@
         <v>66</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>132</v>
-      </c>
       <c r="F21" s="8" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>69</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="7" t="n">
+      <c r="F22" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="str">
-        <f aca="false">CONCATENATE("Всего позиций: ",COUNTA(B12:B22),"; листов копий: ",SUM(K12:K22))</f>
-        <v>Всего позиций: 8; листов копий: 13</v>
-      </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
+      <c r="F24" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G28" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="A27" s="9" t="str">
+        <f aca="false">CONCATENATE("Всего позиций: ",COUNTA(B12:B25),"; листов копий: ",SUM(K12:K25))</f>
+        <v>Всего позиций: 11; листов копий: 26</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="A30" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G32" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
+      <c r="G31" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G35" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1386,19 +1484,19 @@
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A12:L12"/>
     <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A19:L19"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="A30:L30"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:L30"/>
     <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:L31"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="A37:L37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
